--- a/data/trans_orig/P2A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13299</t>
+          <t>14015</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26064</t>
+          <t>25848</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14956</t>
+          <t>14906</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27588</t>
+          <t>27497</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32450</t>
+          <t>32078</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49576</t>
+          <t>49292</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54391</t>
+          <t>54607</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67156</t>
+          <t>66440</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44049</t>
+          <t>44140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56681</t>
+          <t>56731</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>102516</t>
+          <t>102800</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>119642</t>
+          <t>120014</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,91%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19400</t>
+          <t>19150</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32930</t>
+          <t>32848</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23525</t>
+          <t>22481</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36297</t>
+          <t>35956</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45834</t>
+          <t>46191</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64548</t>
+          <t>64535</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,39%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35757</t>
+          <t>35839</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49287</t>
+          <t>49537</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31188</t>
+          <t>31529</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43960</t>
+          <t>45004</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>71624</t>
+          <t>71637</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>90338</t>
+          <t>89981</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,08%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>9969</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20705</t>
+          <t>20844</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17602</t>
+          <t>17916</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29965</t>
+          <t>30233</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30822</t>
+          <t>30627</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46674</t>
+          <t>48097</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,83%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37540</t>
+          <t>37401</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48475</t>
+          <t>48276</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53979</t>
+          <t>53711</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66342</t>
+          <t>66028</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>95515</t>
+          <t>94092</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111367</t>
+          <t>111562</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41862</t>
+          <t>41356</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60842</t>
+          <t>60412</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45781</t>
+          <t>45625</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64270</t>
+          <t>66132</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93172</t>
+          <t>91968</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>119356</t>
+          <t>117933</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,33%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90454</t>
+          <t>90884</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>109434</t>
+          <t>109940</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84292</t>
+          <t>82430</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102781</t>
+          <t>102937</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>180502</t>
+          <t>181925</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>206686</t>
+          <t>207890</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,33%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17927</t>
+          <t>18449</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31103</t>
+          <t>30624</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30316</t>
+          <t>30967</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45130</t>
+          <t>45594</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52682</t>
+          <t>52317</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71884</t>
+          <t>72374</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>47,1%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38020</t>
+          <t>38499</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51196</t>
+          <t>50674</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39400</t>
+          <t>38936</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54214</t>
+          <t>53563</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81768</t>
+          <t>81278</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>100970</t>
+          <t>101335</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,95%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24320</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38029</t>
+          <t>38423</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22095</t>
+          <t>22708</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36290</t>
+          <t>35691</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51518</t>
+          <t>50996</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70965</t>
+          <t>70405</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>47,81%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36841</t>
+          <t>36447</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50236</t>
+          <t>50550</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36102</t>
+          <t>36701</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50297</t>
+          <t>49684</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>76297</t>
+          <t>76857</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>95744</t>
+          <t>96266</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>65,37%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>148553</t>
+          <t>148630</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>182448</t>
+          <t>184110</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>179082</t>
+          <t>179464</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>213526</t>
+          <t>214454</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>337585</t>
+          <t>338454</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>385610</t>
+          <t>388952</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,72%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>320227</t>
+          <t>318565</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>354122</t>
+          <t>354045</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>315023</t>
+          <t>314095</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>349467</t>
+          <t>349085</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>645615</t>
+          <t>642273</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>693640</t>
+          <t>692771</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,18%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15449</t>
+          <t>14709</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27052</t>
+          <t>27387</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12690</t>
+          <t>12457</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25125</t>
+          <t>25421</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30671</t>
+          <t>30901</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47388</t>
+          <t>48307</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34169</t>
+          <t>33834</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45772</t>
+          <t>46512</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48285</t>
+          <t>47989</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60720</t>
+          <t>60953</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87243</t>
+          <t>86324</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103960</t>
+          <t>103730</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,05%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30613</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14675</t>
+          <t>14303</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26840</t>
+          <t>27067</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36461</t>
+          <t>36340</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54163</t>
+          <t>54193</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,47%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34766</t>
+          <t>35386</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47988</t>
+          <t>48471</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41686</t>
+          <t>41459</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53851</t>
+          <t>54223</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79742</t>
+          <t>79712</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>97444</t>
+          <t>97565</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,86%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19141</t>
+          <t>19076</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31823</t>
+          <t>31796</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14686</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27378</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36907</t>
+          <t>37333</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54766</t>
+          <t>54865</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,8%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34700</t>
+          <t>34727</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47382</t>
+          <t>47447</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40586</t>
+          <t>40520</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53278</t>
+          <t>52666</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>79721</t>
+          <t>79622</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>97580</t>
+          <t>97154</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,24%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42684</t>
+          <t>41364</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60812</t>
+          <t>59845</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55228</t>
+          <t>55890</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74936</t>
+          <t>76403</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103082</t>
+          <t>102869</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130543</t>
+          <t>130614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,85%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75668</t>
+          <t>76635</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93796</t>
+          <t>95116</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>86428</t>
+          <t>84961</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>106136</t>
+          <t>105474</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>167301</t>
+          <t>167230</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>194762</t>
+          <t>194975</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,46%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20815</t>
+          <t>20587</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35434</t>
+          <t>35312</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28863</t>
+          <t>29716</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44697</t>
+          <t>45593</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54250</t>
+          <t>54846</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74993</t>
+          <t>75207</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58017</t>
+          <t>58139</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72636</t>
+          <t>72864</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47311</t>
+          <t>46415</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63145</t>
+          <t>62292</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>110466</t>
+          <t>110252</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131209</t>
+          <t>130613</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,43%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14874</t>
+          <t>14949</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26431</t>
+          <t>26707</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20307</t>
+          <t>20889</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34275</t>
+          <t>34991</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39020</t>
+          <t>39933</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58032</t>
+          <t>57396</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>44,86%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27480</t>
+          <t>27204</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39037</t>
+          <t>38962</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39763</t>
+          <t>39047</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53731</t>
+          <t>53149</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>69917</t>
+          <t>70553</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88929</t>
+          <t>88016</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>68,79%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>153090</t>
+          <t>153097</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>187837</t>
+          <t>186219</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>168473</t>
+          <t>170639</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>205540</t>
+          <t>207829</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>332509</t>
+          <t>333783</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>382626</t>
+          <t>381990</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>289128</t>
+          <t>290746</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>323875</t>
+          <t>323868</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>331770</t>
+          <t>329481</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>368837</t>
+          <t>366671</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>631649</t>
+          <t>632285</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>681766</t>
+          <t>680492</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,09%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17696</t>
+          <t>17074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29685</t>
+          <t>30698</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19879</t>
+          <t>19462</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32922</t>
+          <t>33340</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40768</t>
+          <t>40256</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60208</t>
+          <t>59479</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,57%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35146</t>
+          <t>34133</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47135</t>
+          <t>47757</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45332</t>
+          <t>44914</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58375</t>
+          <t>58792</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>83606</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>102317</t>
+          <t>102829</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,87%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18574</t>
+          <t>18857</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32531</t>
+          <t>31598</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21774</t>
+          <t>21878</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36008</t>
+          <t>36293</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44829</t>
+          <t>43190</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64072</t>
+          <t>63272</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,08%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49780</t>
+          <t>50713</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63737</t>
+          <t>63454</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>57059</t>
+          <t>56774</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>71293</t>
+          <t>71189</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>111306</t>
+          <t>112106</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>130549</t>
+          <t>132188</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>75,37%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19599</t>
+          <t>19760</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14789</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>26224</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26720</t>
+          <t>26044</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42010</t>
+          <t>42474</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29625</t>
+          <t>29464</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40105</t>
+          <t>39951</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35388</t>
+          <t>34787</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46222</t>
+          <t>46593</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>68224</t>
+          <t>67760</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>83514</t>
+          <t>84190</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>76,37%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49146</t>
+          <t>49339</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68986</t>
+          <t>69458</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43552</t>
+          <t>43307</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62829</t>
+          <t>62622</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97390</t>
+          <t>97305</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125286</t>
+          <t>125550</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,29%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96811</t>
+          <t>96339</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>116651</t>
+          <t>116458</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108054</t>
+          <t>108261</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127331</t>
+          <t>127576</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>211394</t>
+          <t>211130</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>239290</t>
+          <t>239375</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,1%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29599</t>
+          <t>29609</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44873</t>
+          <t>44655</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35025</t>
+          <t>34972</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51724</t>
+          <t>52036</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69055</t>
+          <t>69894</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>92285</t>
+          <t>92601</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,13%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56706</t>
+          <t>56924</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71980</t>
+          <t>71970</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47429</t>
+          <t>47117</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64128</t>
+          <t>64181</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>108447</t>
+          <t>108131</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131677</t>
+          <t>130838</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15361</t>
+          <t>15596</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27802</t>
+          <t>28063</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13379</t>
+          <t>12721</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25256</t>
+          <t>25001</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32437</t>
+          <t>30777</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49423</t>
+          <t>48592</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>37,92%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32532</t>
+          <t>32271</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44973</t>
+          <t>44738</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42569</t>
+          <t>42824</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54446</t>
+          <t>55104</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78736</t>
+          <t>79567</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>95722</t>
+          <t>97382</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>75,99%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>163061</t>
+          <t>161513</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>197570</t>
+          <t>196742</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>170411</t>
+          <t>170564</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>207208</t>
+          <t>207289</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>344329</t>
+          <t>344168</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>397121</t>
+          <t>394720</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,07%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>326506</t>
+          <t>327334</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>361015</t>
+          <t>362563</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>362984</t>
+          <t>362903</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>399781</t>
+          <t>399628</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>697147</t>
+          <t>699548</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>749939</t>
+          <t>750100</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,55%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70602</t>
+          <t>71373</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86223</t>
+          <t>85790</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>83193</t>
+          <t>84582</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>109415</t>
+          <t>109183</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>160280</t>
+          <t>160795</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>189648</t>
+          <t>189510</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,51%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18239</t>
+          <t>18672</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33860</t>
+          <t>33089</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27493</t>
+          <t>27725</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53715</t>
+          <t>52326</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51722</t>
+          <t>51860</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81090</t>
+          <t>80575</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65601</t>
+          <t>65279</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79176</t>
+          <t>79197</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72373</t>
+          <t>72164</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86266</t>
+          <t>85496</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>141893</t>
+          <t>143394</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>160260</t>
+          <t>161502</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,89%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15505</t>
+          <t>15484</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29080</t>
+          <t>29402</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>10077</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23200</t>
+          <t>23409</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29994</t>
+          <t>28752</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>48361</t>
+          <t>46860</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38749</t>
+          <t>39872</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47718</t>
+          <t>48108</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42432</t>
+          <t>43438</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55609</t>
+          <t>55761</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85585</t>
+          <t>84647</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101485</t>
+          <t>101122</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,39%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13112</t>
+          <t>11989</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21421</t>
+          <t>20415</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14229</t>
+          <t>14592</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30129</t>
+          <t>31067</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>156476</t>
+          <t>156806</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>188648</t>
+          <t>188748</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>152513</t>
+          <t>150658</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>180473</t>
+          <t>179432</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>317760</t>
+          <t>317345</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>361723</t>
+          <t>360141</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30177</t>
+          <t>30077</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62349</t>
+          <t>62019</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37799</t>
+          <t>38840</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65759</t>
+          <t>67614</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>75374</t>
+          <t>76956</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119337</t>
+          <t>119752</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,4%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85994</t>
+          <t>85960</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100444</t>
+          <t>100818</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>85848</t>
+          <t>83058</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>120495</t>
+          <t>120671</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>172144</t>
+          <t>176288</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>216532</t>
+          <t>217892</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>77,25%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18984</t>
+          <t>18610</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33434</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42122</t>
+          <t>41946</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76769</t>
+          <t>79559</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65513</t>
+          <t>64153</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>109901</t>
+          <t>105757</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>37,5%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42261</t>
+          <t>41878</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54980</t>
+          <t>55260</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53449</t>
+          <t>54176</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65601</t>
+          <t>66134</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>101318</t>
+          <t>100918</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>118273</t>
+          <t>118236</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,92%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13915</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26634</t>
+          <t>27017</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6402</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18554</t>
+          <t>17827</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22625</t>
+          <t>22662</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39580</t>
+          <t>39980</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,38%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>488587</t>
+          <t>491320</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>534937</t>
+          <t>536653</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>531423</t>
+          <t>531517</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>588572</t>
+          <t>589345</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1038982</t>
+          <t>1034504</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1114522</t>
+          <t>1107502</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>78,69%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>123216</t>
+          <t>121500</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>169566</t>
+          <t>166833</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>160653</t>
+          <t>159880</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>217802</t>
+          <t>217708</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>292856</t>
+          <t>299876</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>368396</t>
+          <t>372874</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
